--- a/AAII_Financials/Yearly/TLPH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TLPH_YR_FIN.xlsx
@@ -747,10 +747,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>200</v>
+        <v>6000</v>
       </c>
       <c r="E9" s="3">
-        <v>400</v>
+        <v>6700</v>
       </c>
       <c r="F9" s="3">
         <v>5500</v>
@@ -780,10 +780,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-200</v>
+        <v>-6000</v>
       </c>
       <c r="E10" s="3">
-        <v>-400</v>
+        <v>-6700</v>
       </c>
       <c r="F10" s="3">
         <v>-4900</v>
@@ -828,10 +828,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="E12" s="3">
-        <v>6300</v>
+        <v>6700</v>
       </c>
       <c r="F12" s="3">
         <v>5500</v>
